--- a/etf_holdings/2026-09-21_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-21_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,29 +464,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00992A(30,000)</t>
+          <t>00991A(870,000)、00403A(80,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00403A(-127,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,15 +494,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>00992A(30,000)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>00403A(-127,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>全部加碼</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>00403A(78,000)、00405A(120,000)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
